--- a/Final_Figures_and_Sheets_Superset/Kd_pc_values_FullBeta.xlsx
+++ b/Final_Figures_and_Sheets_Superset/Kd_pc_values_FullBeta.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4618,21 +4618,21 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>0.0002880184331797235</v>
+        <v>0.0002511818499292787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B10BR × C57BL6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B10BR × C57BL6</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>B10BR|GYF × B10BR|HFL</t>
+          <t>B10BR × C57BL6</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4642,167 +4642,123 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
+          <t>C57BL6</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>L6: pre-immune</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>B10BR</t>
+        </is>
+      </c>
       <c r="E102" t="n">
-        <v>3.178181571631975e-05</v>
+        <v>9.542409372055383e-06</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>B10BR|GYF × B10BR|SYF</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr"/>
+          <t>B10BR SLO</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>L6: pre-immune</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>C57BL6</t>
+        </is>
+      </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>4.229840548900228e-06</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>C57BL6 SLO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>B10BR|GYF × C57BL6|GYF</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr"/>
+          <t>C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>L6: pre-immune</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>B10BR × C57BL6</t>
+        </is>
+      </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>2.486827862711209e-06</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B10BR × C57BL6 SLO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>B10BR|GYF × C57BL6|HFL</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr"/>
+          <t>B10BR × C57BL6 SLO</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4814,21 +4770,21 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>1.83327466854394e-06</v>
+        <v>1.376727287946367e-07</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>B10BR|GYF × C57BL6|SYF</t>
+          <t>B10BR Kb × B10BR Kd</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4838,621 +4794,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
+          <t>B10BR</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="n">
-        <v>2.870615613086945e-06</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>B10BR|HFL × B10BR|SYF</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>B10BR|HFL × C57BL6|GYF</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>B10BR|HFL × C57BL6|HFL</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="n">
-        <v>4.731031402694038e-07</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>B10BR|HFL × C57BL6|SYF</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="n">
-        <v>3.129184734892553e-05</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>B10BR|SYF × C57BL6|GYF</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="n">
-        <v>2.536018905463165e-05</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>B10BR|SYF × C57BL6|HFL</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="n">
-        <v>0.0007094903480411836</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>B10BR|SYF × C57BL6|SYF</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="n">
-        <v>0.001725327544080326</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>C57BL6|GYF × C57BL6|HFL</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="n">
-        <v>0.0002855137999347472</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>C57BL6|GYF × C57BL6|SYF</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>GYF</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>L5: all supersets</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="n">
-        <v>0.002446759812568519</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>C57BL6|HFL × C57BL6|SYF</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>HFL</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>SYF</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>L6: pre-immune</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>9.542409372055383e-06</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>B10BR SLO</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>B10BR</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>individual</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>L6: pre-immune</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>4.229840548900228e-06</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>C57BL6 SLO</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>C57BL6</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>individual</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>L6: pre-immune</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>B10BR × C57BL6</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>2.486827862711209e-06</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>B10BR × C57BL6</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Final_Figures_and_Sheets_Superset/Kd_pc_values_FullBeta.xlsx
+++ b/Final_Figures_and_Sheets_Superset/Kd_pc_values_FullBeta.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -537,7 +537,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -576,7 +576,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -615,7 +615,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -654,7 +654,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -693,7 +693,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -732,7 +732,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -771,7 +771,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -810,7 +810,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -849,7 +849,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -888,7 +888,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -927,7 +927,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -966,7 +966,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1005,7 +1005,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1044,7 +1044,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1083,7 +1083,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1122,7 +1122,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1161,7 +1161,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1200,7 +1200,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1239,7 +1239,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1278,7 +1278,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1317,7 +1317,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1356,7 +1356,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1395,7 +1395,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1434,7 +1434,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1473,7 +1473,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1512,7 +1512,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1551,8 +1551,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1593,8 +1592,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1635,8 +1633,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1677,8 +1674,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1719,8 +1715,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1761,8 +1756,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1803,8 +1797,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1845,8 +1838,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1887,8 +1879,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1929,8 +1920,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1971,8 +1961,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2013,8 +2002,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2055,8 +2043,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2097,8 +2084,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2139,8 +2125,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2181,8 +2166,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2223,8 +2207,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2265,8 +2248,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2307,8 +2289,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2349,8 +2330,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2391,8 +2371,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2433,8 +2412,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2475,8 +2453,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2517,8 +2494,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2559,8 +2535,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2601,8 +2576,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2643,8 +2617,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2685,8 +2658,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2727,8 +2699,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2769,8 +2740,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2811,8 +2781,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2853,8 +2822,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2895,8 +2863,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2937,8 +2904,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2979,8 +2945,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3021,8 +2986,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3063,8 +3027,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3105,8 +3068,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3147,8 +3109,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3189,8 +3150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3231,8 +3191,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3273,8 +3232,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3315,8 +3273,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3357,8 +3314,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3399,8 +3355,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3441,8 +3396,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3483,8 +3437,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3525,8 +3478,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3567,8 +3519,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3609,8 +3560,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3651,8 +3601,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3693,8 +3642,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3735,8 +3683,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3777,8 +3724,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3819,8 +3765,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3861,8 +3806,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3903,8 +3847,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3945,8 +3888,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3987,8 +3929,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4029,8 +3970,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4071,8 +4011,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4113,8 +4052,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -4155,8 +4093,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -4197,8 +4134,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4243,8 +4179,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4289,8 +4224,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4335,8 +4269,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4381,8 +4314,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4427,8 +4359,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4473,8 +4404,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4519,8 +4449,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4565,8 +4494,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4611,7 +4539,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4726,7 +4654,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4763,7 +4691,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
